--- a/data/experiment_description.xlsx
+++ b/data/experiment_description.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linda\OneDrive\Desktop\ZALF\RapSmartN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7587CC4D-B47A-4E7A-B903-00D854E38276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A8ABA6-219C-4867-A0AA-5115A260401F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="129">
   <si>
     <t>Experiment</t>
   </si>
@@ -270,13 +270,166 @@
   </si>
   <si>
     <t>Erste Modellparametrisierung mit Daten aus Neubrandenburg. Soil1 ist das Leitprofil der BÜK200 Legendeneinheit 45 "Normpseudogley"</t>
+  </si>
+  <si>
+    <t>EX37</t>
+  </si>
+  <si>
+    <t>RapSmartN_MONICA03</t>
+  </si>
+  <si>
+    <t>EX38</t>
+  </si>
+  <si>
+    <t>EX39</t>
+  </si>
+  <si>
+    <t>EX40</t>
+  </si>
+  <si>
+    <t>EX41</t>
+  </si>
+  <si>
+    <t>EX42</t>
+  </si>
+  <si>
+    <t>soil2</t>
+  </si>
+  <si>
+    <t>EX43</t>
+  </si>
+  <si>
+    <t>EX44</t>
+  </si>
+  <si>
+    <t>EX45</t>
+  </si>
+  <si>
+    <t>EX46</t>
+  </si>
+  <si>
+    <t>EX47</t>
+  </si>
+  <si>
+    <t>soil3</t>
+  </si>
+  <si>
+    <t>EX48</t>
+  </si>
+  <si>
+    <t>EX49</t>
+  </si>
+  <si>
+    <t>EX50</t>
+  </si>
+  <si>
+    <t>EX51</t>
+  </si>
+  <si>
+    <t>EX52</t>
+  </si>
+  <si>
+    <t>soil4</t>
+  </si>
+  <si>
+    <t>EX53</t>
+  </si>
+  <si>
+    <t>EX54</t>
+  </si>
+  <si>
+    <t>EX55</t>
+  </si>
+  <si>
+    <t>EX56</t>
+  </si>
+  <si>
+    <t>EX57</t>
+  </si>
+  <si>
+    <t>soil5</t>
+  </si>
+  <si>
+    <t>EX58</t>
+  </si>
+  <si>
+    <t>EX59</t>
+  </si>
+  <si>
+    <t>EX60</t>
+  </si>
+  <si>
+    <t>EX61</t>
+  </si>
+  <si>
+    <t>260224_MONICA_03</t>
+  </si>
+  <si>
+    <t>Modellparameter wie in MONICA_01; Veränderung des Saattermins, Verwendung des Leitprofils der BÜK Legendeneinheit 45</t>
+  </si>
+  <si>
+    <t>Modellparameter wie in MONICA_01; Veränderung des Saattermins, Verwendung des Begleitprofils 2619 der BÜK Legendeneinheit 27</t>
+  </si>
+  <si>
+    <t>Modellparameter wie in MONICA_01; Veränderung des Saattermins, Verwendung des Begleitprofils 2615 der BÜK Legendeneinheit 27</t>
+  </si>
+  <si>
+    <t>Modellparameter wie in MONICA_01; Veränderung des Saattermins, Verwendung des Begleitprofils 2614 der BÜK Legendeneinheit 27</t>
+  </si>
+  <si>
+    <t>Modellparameter wie in MONICA_01; Veränderung des Saattermins, Verwendung des Begleitprofils 4855 der BÜK Legendeneinheit 45</t>
+  </si>
+  <si>
+    <t>EX62</t>
+  </si>
+  <si>
+    <t>RapSmartN_MONICA04</t>
+  </si>
+  <si>
+    <t>260225_MONICA_04</t>
+  </si>
+  <si>
+    <t>Veränderungen im rape.json und winter-rape.json um für diesen Termin 7665 kg DM/ha und 100-110 kg N uptake zu erreichen</t>
+  </si>
+  <si>
+    <t>EX63</t>
+  </si>
+  <si>
+    <t>RapSmartN_MONICA05</t>
+  </si>
+  <si>
+    <t>fert5</t>
+  </si>
+  <si>
+    <t>EX64</t>
+  </si>
+  <si>
+    <t>fert6</t>
+  </si>
+  <si>
+    <t>EX65</t>
+  </si>
+  <si>
+    <t>resi1</t>
+  </si>
+  <si>
+    <t>260225_MONICA_05</t>
+  </si>
+  <si>
+    <t>Modify N-Input by fertilisation (30 kg N)</t>
+  </si>
+  <si>
+    <t>Modify N-Input by fertilisation (100 kg N)</t>
+  </si>
+  <si>
+    <t>Modify residues</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +446,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -317,10 +476,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -603,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2906,6 +3068,1804 @@
         <v>67</v>
       </c>
     </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="1">
+        <v>45885</v>
+      </c>
+      <c r="G38" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" t="s">
+        <v>38</v>
+      </c>
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" t="s">
+        <v>27</v>
+      </c>
+      <c r="N38" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P38">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q38">
+        <v>12.959</v>
+      </c>
+      <c r="R38">
+        <v>40</v>
+      </c>
+      <c r="S38" t="s">
+        <v>108</v>
+      </c>
+      <c r="T38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39">
+        <v>2026</v>
+      </c>
+      <c r="F39" s="1">
+        <v>45890</v>
+      </c>
+      <c r="G39" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>27</v>
+      </c>
+      <c r="N39" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" t="s">
+        <v>29</v>
+      </c>
+      <c r="P39">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q39">
+        <v>12.959</v>
+      </c>
+      <c r="R39">
+        <v>40</v>
+      </c>
+      <c r="S39" t="s">
+        <v>108</v>
+      </c>
+      <c r="T39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>2026</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45895</v>
+      </c>
+      <c r="G40" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" t="s">
+        <v>27</v>
+      </c>
+      <c r="N40" t="s">
+        <v>28</v>
+      </c>
+      <c r="O40" t="s">
+        <v>29</v>
+      </c>
+      <c r="P40">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q40">
+        <v>12.959</v>
+      </c>
+      <c r="R40">
+        <v>40</v>
+      </c>
+      <c r="S40" t="s">
+        <v>108</v>
+      </c>
+      <c r="T40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41">
+        <v>2026</v>
+      </c>
+      <c r="F41" s="1">
+        <v>45900</v>
+      </c>
+      <c r="G41" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" t="s">
+        <v>28</v>
+      </c>
+      <c r="O41" t="s">
+        <v>29</v>
+      </c>
+      <c r="P41">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q41">
+        <v>12.959</v>
+      </c>
+      <c r="R41">
+        <v>40</v>
+      </c>
+      <c r="S41" t="s">
+        <v>108</v>
+      </c>
+      <c r="T41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42">
+        <v>2026</v>
+      </c>
+      <c r="F42" s="1">
+        <v>45905</v>
+      </c>
+      <c r="G42" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H42" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" t="s">
+        <v>27</v>
+      </c>
+      <c r="N42" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" t="s">
+        <v>29</v>
+      </c>
+      <c r="P42">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q42">
+        <v>12.959</v>
+      </c>
+      <c r="R42">
+        <v>40</v>
+      </c>
+      <c r="S42" t="s">
+        <v>108</v>
+      </c>
+      <c r="T42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43">
+        <v>2026</v>
+      </c>
+      <c r="F43" s="1">
+        <v>45885</v>
+      </c>
+      <c r="G43" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" t="s">
+        <v>27</v>
+      </c>
+      <c r="N43" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" t="s">
+        <v>29</v>
+      </c>
+      <c r="P43">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q43">
+        <v>12.959</v>
+      </c>
+      <c r="R43">
+        <v>40</v>
+      </c>
+      <c r="S43" t="s">
+        <v>108</v>
+      </c>
+      <c r="T43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44">
+        <v>2026</v>
+      </c>
+      <c r="F44" s="1">
+        <v>45890</v>
+      </c>
+      <c r="G44" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" t="s">
+        <v>27</v>
+      </c>
+      <c r="N44" t="s">
+        <v>28</v>
+      </c>
+      <c r="O44" t="s">
+        <v>29</v>
+      </c>
+      <c r="P44">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q44">
+        <v>12.959</v>
+      </c>
+      <c r="R44">
+        <v>40</v>
+      </c>
+      <c r="S44" t="s">
+        <v>108</v>
+      </c>
+      <c r="T44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45">
+        <v>2026</v>
+      </c>
+      <c r="F45" s="1">
+        <v>45895</v>
+      </c>
+      <c r="G45" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" t="s">
+        <v>27</v>
+      </c>
+      <c r="N45" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" t="s">
+        <v>29</v>
+      </c>
+      <c r="P45">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q45">
+        <v>12.959</v>
+      </c>
+      <c r="R45">
+        <v>40</v>
+      </c>
+      <c r="S45" t="s">
+        <v>108</v>
+      </c>
+      <c r="T45" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46">
+        <v>2026</v>
+      </c>
+      <c r="F46" s="1">
+        <v>45900</v>
+      </c>
+      <c r="G46" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" t="s">
+        <v>27</v>
+      </c>
+      <c r="N46" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" t="s">
+        <v>29</v>
+      </c>
+      <c r="P46">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q46">
+        <v>12.959</v>
+      </c>
+      <c r="R46">
+        <v>40</v>
+      </c>
+      <c r="S46" t="s">
+        <v>108</v>
+      </c>
+      <c r="T46" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47">
+        <v>2026</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45905</v>
+      </c>
+      <c r="G47" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" t="s">
+        <v>27</v>
+      </c>
+      <c r="N47" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" t="s">
+        <v>29</v>
+      </c>
+      <c r="P47">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q47">
+        <v>12.959</v>
+      </c>
+      <c r="R47">
+        <v>40</v>
+      </c>
+      <c r="S47" t="s">
+        <v>108</v>
+      </c>
+      <c r="T47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48">
+        <v>2026</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45885</v>
+      </c>
+      <c r="G48" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" t="s">
+        <v>27</v>
+      </c>
+      <c r="N48" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" t="s">
+        <v>29</v>
+      </c>
+      <c r="P48">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q48">
+        <v>12.959</v>
+      </c>
+      <c r="R48">
+        <v>40</v>
+      </c>
+      <c r="S48" t="s">
+        <v>108</v>
+      </c>
+      <c r="T48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49">
+        <v>2026</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45890</v>
+      </c>
+      <c r="G49" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" t="s">
+        <v>27</v>
+      </c>
+      <c r="N49" t="s">
+        <v>28</v>
+      </c>
+      <c r="O49" t="s">
+        <v>29</v>
+      </c>
+      <c r="P49">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q49">
+        <v>12.959</v>
+      </c>
+      <c r="R49">
+        <v>40</v>
+      </c>
+      <c r="S49" t="s">
+        <v>108</v>
+      </c>
+      <c r="T49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50">
+        <v>2026</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45895</v>
+      </c>
+      <c r="G50" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H50" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" t="s">
+        <v>38</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" t="s">
+        <v>29</v>
+      </c>
+      <c r="P50">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q50">
+        <v>12.959</v>
+      </c>
+      <c r="R50">
+        <v>40</v>
+      </c>
+      <c r="S50" t="s">
+        <v>108</v>
+      </c>
+      <c r="T50" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51">
+        <v>2026</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45900</v>
+      </c>
+      <c r="G51" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" t="s">
+        <v>27</v>
+      </c>
+      <c r="N51" t="s">
+        <v>28</v>
+      </c>
+      <c r="O51" t="s">
+        <v>29</v>
+      </c>
+      <c r="P51">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q51">
+        <v>12.959</v>
+      </c>
+      <c r="R51">
+        <v>40</v>
+      </c>
+      <c r="S51" t="s">
+        <v>108</v>
+      </c>
+      <c r="T51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52">
+        <v>2026</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45905</v>
+      </c>
+      <c r="G52" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H52" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" t="s">
+        <v>27</v>
+      </c>
+      <c r="N52" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" t="s">
+        <v>29</v>
+      </c>
+      <c r="P52">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q52">
+        <v>12.959</v>
+      </c>
+      <c r="R52">
+        <v>40</v>
+      </c>
+      <c r="S52" t="s">
+        <v>108</v>
+      </c>
+      <c r="T52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53">
+        <v>2026</v>
+      </c>
+      <c r="F53" s="1">
+        <v>45885</v>
+      </c>
+      <c r="G53" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N53" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" t="s">
+        <v>29</v>
+      </c>
+      <c r="P53">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q53">
+        <v>12.959</v>
+      </c>
+      <c r="R53">
+        <v>40</v>
+      </c>
+      <c r="S53" t="s">
+        <v>108</v>
+      </c>
+      <c r="T53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54">
+        <v>2026</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45890</v>
+      </c>
+      <c r="G54" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H54" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" t="s">
+        <v>37</v>
+      </c>
+      <c r="J54" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" t="s">
+        <v>28</v>
+      </c>
+      <c r="O54" t="s">
+        <v>29</v>
+      </c>
+      <c r="P54">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q54">
+        <v>12.959</v>
+      </c>
+      <c r="R54">
+        <v>40</v>
+      </c>
+      <c r="S54" t="s">
+        <v>108</v>
+      </c>
+      <c r="T54" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55">
+        <v>2026</v>
+      </c>
+      <c r="F55" s="1">
+        <v>45895</v>
+      </c>
+      <c r="G55" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" t="s">
+        <v>37</v>
+      </c>
+      <c r="J55" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" t="s">
+        <v>29</v>
+      </c>
+      <c r="P55">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q55">
+        <v>12.959</v>
+      </c>
+      <c r="R55">
+        <v>40</v>
+      </c>
+      <c r="S55" t="s">
+        <v>108</v>
+      </c>
+      <c r="T55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56">
+        <v>2026</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45900</v>
+      </c>
+      <c r="G56" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H56" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" t="s">
+        <v>28</v>
+      </c>
+      <c r="O56" t="s">
+        <v>29</v>
+      </c>
+      <c r="P56">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q56">
+        <v>12.959</v>
+      </c>
+      <c r="R56">
+        <v>40</v>
+      </c>
+      <c r="S56" t="s">
+        <v>108</v>
+      </c>
+      <c r="T56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57">
+        <v>2026</v>
+      </c>
+      <c r="F57" s="1">
+        <v>45905</v>
+      </c>
+      <c r="G57" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H57" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" t="s">
+        <v>37</v>
+      </c>
+      <c r="J57" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" t="s">
+        <v>28</v>
+      </c>
+      <c r="O57" t="s">
+        <v>29</v>
+      </c>
+      <c r="P57">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q57">
+        <v>12.959</v>
+      </c>
+      <c r="R57">
+        <v>40</v>
+      </c>
+      <c r="S57" t="s">
+        <v>108</v>
+      </c>
+      <c r="T57" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58">
+        <v>2026</v>
+      </c>
+      <c r="F58" s="1">
+        <v>45885</v>
+      </c>
+      <c r="G58" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H58" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" t="s">
+        <v>37</v>
+      </c>
+      <c r="J58" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" t="s">
+        <v>38</v>
+      </c>
+      <c r="L58" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" t="s">
+        <v>27</v>
+      </c>
+      <c r="N58" t="s">
+        <v>28</v>
+      </c>
+      <c r="O58" t="s">
+        <v>29</v>
+      </c>
+      <c r="P58">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q58">
+        <v>12.959</v>
+      </c>
+      <c r="R58">
+        <v>40</v>
+      </c>
+      <c r="S58" t="s">
+        <v>108</v>
+      </c>
+      <c r="T58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" t="s">
+        <v>103</v>
+      </c>
+      <c r="E59">
+        <v>2026</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45890</v>
+      </c>
+      <c r="G59" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H59" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" t="s">
+        <v>37</v>
+      </c>
+      <c r="J59" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" t="s">
+        <v>27</v>
+      </c>
+      <c r="N59" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" t="s">
+        <v>29</v>
+      </c>
+      <c r="P59">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q59">
+        <v>12.959</v>
+      </c>
+      <c r="R59">
+        <v>40</v>
+      </c>
+      <c r="S59" t="s">
+        <v>108</v>
+      </c>
+      <c r="T59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" t="s">
+        <v>103</v>
+      </c>
+      <c r="E60">
+        <v>2026</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45895</v>
+      </c>
+      <c r="G60" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H60" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" t="s">
+        <v>38</v>
+      </c>
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" t="s">
+        <v>27</v>
+      </c>
+      <c r="N60" t="s">
+        <v>28</v>
+      </c>
+      <c r="O60" t="s">
+        <v>29</v>
+      </c>
+      <c r="P60">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q60">
+        <v>12.959</v>
+      </c>
+      <c r="R60">
+        <v>40</v>
+      </c>
+      <c r="S60" t="s">
+        <v>108</v>
+      </c>
+      <c r="T60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61">
+        <v>2026</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45900</v>
+      </c>
+      <c r="G61" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H61" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" t="s">
+        <v>38</v>
+      </c>
+      <c r="L61" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" t="s">
+        <v>27</v>
+      </c>
+      <c r="N61" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" t="s">
+        <v>29</v>
+      </c>
+      <c r="P61">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q61">
+        <v>12.959</v>
+      </c>
+      <c r="R61">
+        <v>40</v>
+      </c>
+      <c r="S61" t="s">
+        <v>108</v>
+      </c>
+      <c r="T61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" t="s">
+        <v>103</v>
+      </c>
+      <c r="E62">
+        <v>2026</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45905</v>
+      </c>
+      <c r="G62" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H62" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" t="s">
+        <v>37</v>
+      </c>
+      <c r="J62" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" t="s">
+        <v>38</v>
+      </c>
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" t="s">
+        <v>27</v>
+      </c>
+      <c r="N62" t="s">
+        <v>28</v>
+      </c>
+      <c r="O62" t="s">
+        <v>29</v>
+      </c>
+      <c r="P62">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q62">
+        <v>12.959</v>
+      </c>
+      <c r="R62">
+        <v>40</v>
+      </c>
+      <c r="S62" t="s">
+        <v>108</v>
+      </c>
+      <c r="T62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63">
+        <v>2026</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45889</v>
+      </c>
+      <c r="G63" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H63" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" t="s">
+        <v>37</v>
+      </c>
+      <c r="J63" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" t="s">
+        <v>38</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>27</v>
+      </c>
+      <c r="N63" t="s">
+        <v>28</v>
+      </c>
+      <c r="O63" t="s">
+        <v>29</v>
+      </c>
+      <c r="P63">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q63">
+        <v>12.959</v>
+      </c>
+      <c r="R63">
+        <v>40</v>
+      </c>
+      <c r="S63" t="s">
+        <v>116</v>
+      </c>
+      <c r="T63" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>118</v>
+      </c>
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64">
+        <v>2026</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45889</v>
+      </c>
+      <c r="G64" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H64" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" t="s">
+        <v>37</v>
+      </c>
+      <c r="J64" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" t="s">
+        <v>120</v>
+      </c>
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" t="s">
+        <v>27</v>
+      </c>
+      <c r="N64" t="s">
+        <v>28</v>
+      </c>
+      <c r="O64" t="s">
+        <v>29</v>
+      </c>
+      <c r="P64">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q64">
+        <v>12.959</v>
+      </c>
+      <c r="R64">
+        <v>40</v>
+      </c>
+      <c r="S64" t="s">
+        <v>125</v>
+      </c>
+      <c r="T64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65">
+        <v>2026</v>
+      </c>
+      <c r="F65" s="1">
+        <v>45889</v>
+      </c>
+      <c r="G65" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" t="s">
+        <v>37</v>
+      </c>
+      <c r="J65" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" t="s">
+        <v>122</v>
+      </c>
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>27</v>
+      </c>
+      <c r="N65" t="s">
+        <v>28</v>
+      </c>
+      <c r="O65" t="s">
+        <v>29</v>
+      </c>
+      <c r="P65">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q65">
+        <v>12.959</v>
+      </c>
+      <c r="R65">
+        <v>40</v>
+      </c>
+      <c r="S65" t="s">
+        <v>125</v>
+      </c>
+      <c r="T65" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>119</v>
+      </c>
+      <c r="C66" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66">
+        <v>2026</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45889</v>
+      </c>
+      <c r="G66" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H66" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" t="s">
+        <v>37</v>
+      </c>
+      <c r="J66" t="s">
+        <v>24</v>
+      </c>
+      <c r="K66" t="s">
+        <v>38</v>
+      </c>
+      <c r="L66" t="s">
+        <v>124</v>
+      </c>
+      <c r="M66" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" t="s">
+        <v>28</v>
+      </c>
+      <c r="O66" t="s">
+        <v>29</v>
+      </c>
+      <c r="P66">
+        <v>52.466999999999999</v>
+      </c>
+      <c r="Q66">
+        <v>12.959</v>
+      </c>
+      <c r="R66">
+        <v>40</v>
+      </c>
+      <c r="S66" t="s">
+        <v>125</v>
+      </c>
+      <c r="T66" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
